--- a/prix/hammerite.xlsx
+++ b/prix/hammerite.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA3239D-315D-478D-AE5C-9280802E50F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5368B23F-DB1C-4716-AB00-A166A74B77FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1338,13 +1338,13 @@
         <v>180</v>
       </c>
       <c r="D3" s="11">
-        <v>20.5</v>
+        <v>19.88</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1898,13 +1898,13 @@
         <v>208</v>
       </c>
       <c r="D31" s="11">
-        <v>55</v>
+        <v>53.6</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F31" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/hammerite.xlsx
+++ b/prix/hammerite.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5368B23F-DB1C-4716-AB00-A166A74B77FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E49AF4-23F9-45D2-AFC0-DC1E97911090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="273">
   <si>
     <t>path</t>
   </si>
@@ -1584,7 +1584,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1624,7 +1624,7 @@
         <v>21</v>
       </c>
       <c r="F17" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1698,13 +1698,13 @@
         <v>198</v>
       </c>
       <c r="D21" s="11">
-        <v>51.5</v>
+        <v>56</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1904,7 +1904,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2644,7 +2644,7 @@
         <v>72</v>
       </c>
       <c r="F68" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2778,7 +2778,7 @@
         <v>259</v>
       </c>
       <c r="D75" s="11">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>79</v>
@@ -2798,7 +2798,7 @@
         <v>259</v>
       </c>
       <c r="D76" s="11">
-        <v>67.5</v>
+        <v>72</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>80</v>
@@ -2938,13 +2938,13 @@
         <v>253</v>
       </c>
       <c r="D83" s="11">
-        <v>54.32</v>
+        <v>60</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>87</v>
       </c>
       <c r="F83" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3048,7 +3048,9 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="5"/>
+      <c r="A89" s="5" t="s">
+        <v>271</v>
+      </c>
       <c r="B89" s="9" t="s">
         <v>178</v>
       </c>

--- a/prix/hammerite.xlsx
+++ b/prix/hammerite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E49AF4-23F9-45D2-AFC0-DC1E97911090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7662AD6A-84EE-432C-A74D-D7E185362ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22824" yWindow="660" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -934,10 +934,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1317,13 +1317,13 @@
       <c r="C2" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>20.5</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1337,13 +1337,13 @@
       <c r="C3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>19.88</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1357,13 +1357,13 @@
       <c r="C4" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>22</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <v>7</v>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
       <c r="C5" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>22</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1397,13 +1397,13 @@
       <c r="C6" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>20.5</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1417,13 +1417,13 @@
       <c r="C7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>20.5</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1437,13 +1437,13 @@
       <c r="C8" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>20.5</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="C9" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>20.5</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1477,13 +1477,13 @@
       <c r="C10" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>20.5</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1497,13 +1497,13 @@
       <c r="C11" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>20.5</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1517,13 +1517,13 @@
       <c r="C12" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>20.5</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1537,13 +1537,13 @@
       <c r="C13" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>51.5</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="11">
         <v>4</v>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
       <c r="C14" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>51.5</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1577,14 +1577,14 @@
       <c r="C15" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>55</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="10">
-        <v>2</v>
+      <c r="F15" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1597,13 +1597,13 @@
       <c r="C16" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>54.980000000000004</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1617,13 +1617,13 @@
       <c r="C17" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <v>51.5</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1637,13 +1637,13 @@
       <c r="C18" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <v>51.5</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1657,13 +1657,13 @@
       <c r="C19" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>51.5</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1677,13 +1677,13 @@
       <c r="C20" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <v>51.5</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1697,13 +1697,13 @@
       <c r="C21" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>56</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="11">
         <v>4</v>
       </c>
     </row>
@@ -1717,13 +1717,13 @@
       <c r="C22" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <v>22</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1737,13 +1737,13 @@
       <c r="C23" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>22</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1757,14 +1757,14 @@
       <c r="C24" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <v>22</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="10">
-        <v>4</v>
+      <c r="F24" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1777,13 +1777,13 @@
       <c r="C25" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>22</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1797,13 +1797,13 @@
       <c r="C26" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <v>22</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1817,13 +1817,13 @@
       <c r="C27" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>22</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1837,13 +1837,13 @@
       <c r="C28" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <v>22</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1857,13 +1857,13 @@
       <c r="C29" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <v>55</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1877,13 +1877,13 @@
       <c r="C30" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <v>51.5</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1897,14 +1897,14 @@
       <c r="C31" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <v>53.6</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F31" s="10">
-        <v>1</v>
+      <c r="F31" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1917,13 +1917,13 @@
       <c r="C32" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <v>51.5</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1937,13 +1937,13 @@
       <c r="C33" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>51.5</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1957,13 +1957,13 @@
       <c r="C34" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <v>51.5</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1977,13 +1977,13 @@
       <c r="C35" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <v>51.5</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1997,14 +1997,14 @@
       <c r="C36" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <v>22</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="10">
-        <v>3</v>
+      <c r="F36" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2017,13 +2017,13 @@
       <c r="C37" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>19.920000000000002</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2037,13 +2037,13 @@
       <c r="C38" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <v>29.28</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2057,13 +2057,13 @@
       <c r="C39" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <v>20.5</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2077,13 +2077,13 @@
       <c r="C40" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <v>22</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2097,13 +2097,13 @@
       <c r="C41" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <v>22</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2117,14 +2117,14 @@
       <c r="C42" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <v>20.5</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="10">
-        <v>2</v>
+      <c r="F42" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2137,13 +2137,13 @@
       <c r="C43" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <v>29.25</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2157,13 +2157,13 @@
       <c r="C44" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="10">
         <v>20.47</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2177,13 +2177,13 @@
       <c r="C45" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <v>22</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2197,13 +2197,13 @@
       <c r="C46" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="10">
         <v>54.56</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2217,13 +2217,13 @@
       <c r="C47" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <v>55</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2237,13 +2237,13 @@
       <c r="C48" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="10">
         <v>54.56</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2257,13 +2257,13 @@
       <c r="C49" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <v>51.5</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2277,13 +2277,13 @@
       <c r="C50" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="10">
         <v>19.920000000000002</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2297,13 +2297,13 @@
       <c r="C51" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="10">
         <v>51.5</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2317,13 +2317,13 @@
       <c r="C52" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="10">
         <v>51.5</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2337,13 +2337,13 @@
       <c r="C53" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <v>54.56</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2357,13 +2357,13 @@
       <c r="C54" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="10">
         <v>54.56</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2377,13 +2377,13 @@
       <c r="C55" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <v>51.5</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2397,13 +2397,13 @@
       <c r="C56" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="10">
         <v>42.99</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="10">
+      <c r="F56" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2417,13 +2417,13 @@
       <c r="C57" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <v>132.22</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2437,13 +2437,13 @@
       <c r="C58" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="10">
         <v>30.61</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2457,13 +2457,13 @@
       <c r="C59" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="10">
         <v>15.38</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2477,13 +2477,13 @@
       <c r="C60" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="10">
         <v>29.150000000000002</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F60" s="10">
+      <c r="F60" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2497,14 +2497,14 @@
       <c r="C61" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <v>45.6</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="10">
-        <v>6</v>
+      <c r="F61" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2517,13 +2517,13 @@
       <c r="C62" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="10">
         <v>33.28</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2537,13 +2537,13 @@
       <c r="C63" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <v>25.22</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2557,13 +2557,13 @@
       <c r="C64" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="10">
         <v>24.330000000000002</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="10">
+      <c r="F64" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2577,13 +2577,13 @@
       <c r="C65" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <v>22.98</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="10">
+      <c r="F65" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2597,13 +2597,13 @@
       <c r="C66" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="10">
         <v>26</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="10">
+      <c r="F66" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2617,13 +2617,13 @@
       <c r="C67" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <v>32.14</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="10">
+      <c r="F67" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2637,13 +2637,13 @@
       <c r="C68" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="10">
         <v>48.21</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F68" s="10">
+      <c r="F68" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2657,13 +2657,13 @@
       <c r="C69" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <v>48.5</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2677,13 +2677,13 @@
       <c r="C70" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="10">
         <v>48.21</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
       <c r="C71" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <v>19.920000000000002</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F71" s="10">
+      <c r="F71" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="C72" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="10">
         <v>20.5</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F72" s="10">
+      <c r="F72" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2737,13 +2737,13 @@
       <c r="C73" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <v>22.95</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F73" s="10">
+      <c r="F73" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2757,13 +2757,13 @@
       <c r="C74" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="10">
         <v>34.049999999999997</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F74" s="10">
+      <c r="F74" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2777,13 +2777,13 @@
       <c r="C75" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <v>72</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F75" s="10">
+      <c r="F75" s="11">
         <v>7</v>
       </c>
     </row>
@@ -2797,13 +2797,13 @@
       <c r="C76" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="10">
         <v>72</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F76" s="10">
+      <c r="F76" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2817,13 +2817,13 @@
       <c r="C77" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <v>57.5</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F77" s="10">
+      <c r="F77" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2837,13 +2837,13 @@
       <c r="C78" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="10">
         <v>57.5</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F78" s="10">
+      <c r="F78" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2857,13 +2857,13 @@
       <c r="C79" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <v>57.5</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F79" s="10">
+      <c r="F79" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2877,13 +2877,13 @@
       <c r="C80" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="10">
         <v>57.5</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F80" s="10">
+      <c r="F80" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2897,13 +2897,13 @@
       <c r="C81" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <v>57.5</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F81" s="10">
+      <c r="F81" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2917,13 +2917,13 @@
       <c r="C82" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="10">
         <v>53.28</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F82" s="10">
+      <c r="F82" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2937,13 +2937,13 @@
       <c r="C83" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <v>60</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F83" s="10">
+      <c r="F83" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2957,13 +2957,13 @@
       <c r="C84" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="10">
         <v>51.49</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F84" s="10">
+      <c r="F84" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2977,13 +2977,13 @@
       <c r="C85" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="10">
         <v>20.21</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F85" s="10">
+      <c r="F85" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2997,13 +2997,13 @@
       <c r="C86" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="10">
         <v>20.21</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F86" s="10">
+      <c r="F86" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3017,13 +3017,13 @@
       <c r="C87" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <v>20.21</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F87" s="10">
+      <c r="F87" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3037,13 +3037,13 @@
       <c r="C88" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="10">
         <v>20.21</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F88" s="10">
+      <c r="F88" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3057,13 +3057,13 @@
       <c r="C89" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <v>22.5</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F89" s="10">
+      <c r="F89" s="11">
         <v>3</v>
       </c>
     </row>

--- a/prix/hammerite.xlsx
+++ b/prix/hammerite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7662AD6A-84EE-432C-A74D-D7E185362ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01C697A-3678-4307-A92F-842C8AB3208E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22824" yWindow="660" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="21768" yWindow="84" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1904,7 +1904,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1964,7 +1964,7 @@
         <v>38</v>
       </c>
       <c r="F34" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2104,7 +2104,7 @@
         <v>45</v>
       </c>
       <c r="F41" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2124,7 +2124,7 @@
         <v>46</v>
       </c>
       <c r="F42" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2504,7 +2504,7 @@
         <v>65</v>
       </c>
       <c r="F61" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2764,7 +2764,7 @@
         <v>78</v>
       </c>
       <c r="F74" s="11">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2804,7 +2804,7 @@
         <v>80</v>
       </c>
       <c r="F76" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2884,7 +2884,7 @@
         <v>84</v>
       </c>
       <c r="F80" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2944,7 +2944,7 @@
         <v>87</v>
       </c>
       <c r="F83" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/hammerite.xlsx
+++ b/prix/hammerite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01C697A-3678-4307-A92F-842C8AB3208E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495DBCDB-69ED-4073-BE15-CAE90A926FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21768" yWindow="84" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1344,7 +1344,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1604,7 +1604,7 @@
         <v>20</v>
       </c>
       <c r="F16" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1864,7 +1864,7 @@
         <v>33</v>
       </c>
       <c r="F29" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1898,13 +1898,13 @@
         <v>208</v>
       </c>
       <c r="D31" s="10">
-        <v>53.6</v>
+        <v>56</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F31" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2104,7 +2104,7 @@
         <v>45</v>
       </c>
       <c r="F41" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2238,13 +2238,13 @@
         <v>224</v>
       </c>
       <c r="D48" s="10">
-        <v>54.56</v>
+        <v>60</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>52</v>
       </c>
       <c r="F48" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2758,13 +2758,13 @@
         <v>258</v>
       </c>
       <c r="D74" s="10">
-        <v>34.049999999999997</v>
+        <v>40</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F74" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2784,7 +2784,7 @@
         <v>79</v>
       </c>
       <c r="F75" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2818,13 +2818,13 @@
         <v>247</v>
       </c>
       <c r="D77" s="10">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>81</v>
       </c>
       <c r="F77" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2944,7 +2944,7 @@
         <v>87</v>
       </c>
       <c r="F83" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2964,7 +2964,7 @@
         <v>88</v>
       </c>
       <c r="F84" s="11">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
